--- a/human_validation/judge/kor/judge_D022_S001_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D022_S001_P002__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,208 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 [Name] 선생님입니다. 먼저, 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가... 먹고 나서 일부러 토를 하고 있어요. 가끔은 회사 화장실에서 하기도 하고, 집에 오자마자 하기도 해요. 정말 싫은데, 이게 저를 진정시킬 수 있는 유일한 방법처럼 느껴지기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 먹고 나서 토를 하실 때, 보통 짧은 시간에 아주 많은 양을 먹고 멈출 수 없다는 느낌이 든 후에 그러시는 건가요, 아니면 보통 양의 식사를 한 후에도 그러시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 보통은 양이 정말 많아요. 그러니까, 과자 한 봉지를 다 먹고, 동네 가게에서 산 페이스트리랑 남은 음식, 단 음료까지... 한 자리에서 다 먹어버려요. 얼마나 먹었는지는 다 먹고 나서야 알아차리는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 지금 키와 몸무게가 어떻게 되시는지, 아니면 BMI를 알고 계시면 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 제 BMI는 잘 모르겠어요. 지금 정확한 몸무게도 잘 모르고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 최근에 체중이 눈에 띄게 줄었나요, 아니면 폭식 사이사이에 먹는 양을 자주 제한하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네, 어떻게든 만회하려고 해요. 다음 날은 아주 늦게까지 아무것도 안 먹고, 세탁소에서 하루 종일 서 있어서 다리가 이미 아픈 상태여도 걷거나 운동을 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 이런 폭식-제거 행동이 일주일에 몇 번 정도 일어나는 것 같으세요? 그리고 이 패턴이 얼마나 오래 지속되고 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 몇 달째 그래요. 거의 매주 적어도 두어 번은 그래요, 계획했던 것보다 훨씬 많이 먹고 나서 토를 하거나 굶거나 운동을 해서 없애려고 하는 거요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 본인에 대한 생각, 그러니까 자존감이 체중이나 몸매에 많이 좌우된다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네. 가게에서 잘 지내다가도, 유리에 비친 제 모습을 보고 배나 엉덩이가 커 보이면 그냥 실패자가 된 기분이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 지금 저체중이신지 알고 계신가요, 아니면 의사 같은 분이 키에 비해 체중이 많이 낮다고 말씀하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 제 키에 몸무게가 어느 정도여야 하는지 잘 모르겠어요. 의사 선생님이 저체중이 심하다고 하신 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023) | 배제됨: 신경성 식욕부진증 (D021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 정확하지 않아도 괜찮으니, 대략적으로라도 현재 체중과 키를 말씀해 주실 수 있을까요? BMI를 가늠해보려고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 최근에 몸무게를 재본 적이 없고, 정확한 키도 잘 몰라요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023) | 배제됨: 신경성 식욕부진증 (D021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 요즘 옷이 헐렁해진 걸 느끼셨나요, 아니면 누가 많이 말랐다고 말한 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 옷이 헐렁해진 건 딱히 못 느꼈어요. 많이 말랐다고 한 사람도 없고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 신경성 식욕부진증 (D021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>진단명: 신경성 폭식증 (D022)
 인구통계: 성별 여성 / 나이 36 / 직업상태 laundry or dry cleaning worker / 최종학력 고등학교 중퇴
@@ -575,275 +768,41 @@
 증상 지속 기간: 6 months
 추가 요건: The binge eating and inappropriate compensatory behaviors both occur, on average, at least once a week for 3 months
 주호소 증상 코드: S048
-배경 서술: Daphne는 지속가능한 섬유 전시회를 준비하며 개인적인 습관을 전면적으로 바꾸기로 결심했다. 옷차림을 바꾸고, 금연을 시도했으며, 퇴근 후 함께 식사하던 사람들과 거리를 두고, 친환경 의류 관리 사업의 세련된 얼굴로 자신을 내세우기 시작했다. 처음에는 이런 변화가 힘이 되는 것처럼 느껴졌지만, 6개월이 지나면서 자신이 홍보하는 미학을 직접 구현해야 한다는 압박감이 체중과 체형에 대한 경직된 판단과 뒤엉키게 되었고, 그 뒤를 이어 의도한 것보다 훨씬 많이 먹고 통제력을 되찾지 못하는 일이 반복되었다. 체중 증가를 막기 위해 그는 제거 행동과 비제거성 보상 행동을 번갈아가며 했고, 주변 사람들이 너무 말랐다고 말할 때조차 체중이 늘 것에 대한 두려움은 사라지지 않았다. Daphne는 한 아트센터 오프닝 행사를 앞두고 이 패턴에 대해 일기를 쓰다가, 이 문제가 더 이상 개인적인 절제가 아니라 자신의 하루하루를 지배하는 힘이 되어버렸다는 것을 깨닫고 곧바로 정신건강의학과 진료를 받기로 했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 [Name] 선생님입니다. 먼저, 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가... 먹고 나서 일부러 토를 하고 있어요. 가끔은 회사 화장실에서 하기도 하고, 집에 오자마자 하기도 해요. 정말 싫은데, 이게 저를 진정시킬 수 있는 유일한 방법처럼 느껴지기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 먹고 나서 토를 하실 때, 보통 짧은 시간에 아주 많은 양을 먹고 멈출 수 없다는 느낌이 든 후에 그러시는 건가요, 아니면 보통 양의 식사를 한 후에도 그러시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 보통은 양이 정말 많아요. 그러니까, 과자 한 봉지를 다 먹고, 동네 가게에서 산 페이스트리랑 남은 음식, 단 음료까지... 한 자리에서 다 먹어버려요. 얼마나 먹었는지는 다 먹고 나서야 알아차리는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 지금 키와 몸무게가 어떻게 되시는지, 아니면 BMI를 알고 계시면 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 제 BMI는 잘 모르겠어요. 지금 정확한 몸무게도 잘 모르고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 최근에 체중이 눈에 띄게 줄었나요, 아니면 폭식 사이사이에 먹는 양을 자주 제한하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네, 어떻게든 만회하려고 해요. 다음 날은 아주 늦게까지 아무것도 안 먹고, 세탁소에서 하루 종일 서 있어서 다리가 이미 아픈 상태여도 걷거나 운동을 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 이런 폭식-제거 행동이 일주일에 몇 번 정도 일어나는 것 같으세요? 그리고 이 패턴이 얼마나 오래 지속되고 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 몇 달째 그래요. 거의 매주 적어도 두어 번은 그래요, 계획했던 것보다 훨씬 많이 먹고 나서 토를 하거나 굶거나 운동을 해서 없애려고 하는 거요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 본인에 대한 생각, 그러니까 자존감이 체중이나 몸매에 많이 좌우된다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네. 가게에서 잘 지내다가도, 유리에 비친 제 모습을 보고 배나 엉덩이가 커 보이면 그냥 실패자가 된 기분이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 지금 저체중이신지 알고 계신가요, 아니면 의사 같은 분이 키에 비해 체중이 많이 낮다고 말씀하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 제 키에 몸무게가 어느 정도여야 하는지 잘 모르겠어요. 의사 선생님이 저체중이 심하다고 하신 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023) | 배제됨: 신경성 식욕부진증 (D021)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 정확하지 않아도 괜찮으니, 대략적으로라도 현재 체중과 키를 말씀해 주실 수 있을까요? BMI를 가늠해보려고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 최근에 몸무게를 재본 적이 없고, 정확한 키도 잘 몰라요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023) | 배제됨: 신경성 식욕부진증 (D021)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 요즘 옷이 헐렁해진 걸 느끼셨나요, 아니면 누가 많이 말랐다고 말한 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 옷이 헐렁해진 건 딱히 못 느꼈어요. 많이 말랐다고 한 사람도 없고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
+배경 서술: Daphne는 지속가능한 섬유 전시회를 준비하며 개인적인 습관을 전면적으로 바꾸기로 결심했다. 옷차림을 바꾸고, 금연을 시도했으며, 퇴근 후 함께 식사하던 사람들과 거리를 두고, 친환경 의류 관리 사업의 세련된 얼굴로 자신을 내세우기 시작했다. 처음에는 이런 변화가 힘이 되는 것처럼 느껴졌지만, 6개월이 지나면서 자신이 홍보하는 미학을 직접 구현해야 한다는 압박감이 체중과 체형에 대한 경직된 판단과 뒤엉키게 되었고, 그 뒤를 이어 의도한 것보다 훨씬 많이 먹고 통제력을 되찾지 못하는 일이 반복되었다. 체중 증가를 막기 위해 그는 제거 행동과 비제거성 보상 행동을 번갈아가며 했고, 주변 사람들이 너무 말랐다고 말할 때조차 체중이 늘 것에 대한 두려움은 사라지지 않았다. Daphne는 한 아트센터 오프닝 행사를 앞두고 이 패턴에 대해 일기를 쓰다가, 이 문제가 더 이상 개인적인 절제가 아니라 자신의 하루하루를 지배하는 힘이 되어버렸다는 것을 깨닫고 곧바로 정신건강의학과 진료를 받기로 했다.
+표집된 증상 목록:
+  - S045 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.
+  - S046 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.
+  - S047 비배출성 보상행동: 배출(음식물을 직접 제거하는 행위) 없이 체중 증가를 막기 위한 반복적이고 부적절한 보상 행동.
+  - S048 배출성 보상행동: 체중 증가를 막기 위해 음식이나 체액을 배출하는 반복적이고 부적절한 보상 행동.
+  - S049 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
+  - S050 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).</t>
+        </is>
+      </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 신경성 식욕부진증 (D021)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 신경성 폭식증 (D022, ICD: F50.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
-  확인된 근거: 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
-  누락: 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: compensatory_behavior (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 비배출성 보상행동: 배출(음식물을 직접 제거하는 행위) 없이 체중 증가를 막기 위한 반복적이고 부적절한 보상 행동.; 배출성 보상행동: 체중 증가를 막기 위해 음식이나 체액을 배출하는 반복적이고 부적절한 보상 행동.
-  누락: (없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: body_image_cognition (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.
-  누락: 체중 증가에 대한 두려움: 현저히 낮은 체중임에도 체중이 늘거나 살이 찌는 것에 대한 강한 두려움.</t>
+          <t>의사의 최종 진단: 신경성 폭식증 (D022, ICD: F50.2)
+지속 기간 요건: 있음
+기능적 손상 요건: None
+추가 요건: 있음
+체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
+확인된 근거:
+  - 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
+체크리스트 그룹: compensatory_behavior (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 비배출성 보상행동: 배출(음식물을 직접 제거하는 행위) 없이 체중 증가를 막기 위한 반복적이고 부적절한 보상 행동.
+  - 배출성 보상행동: 체중 증가를 막기 위해 음식이나 체액을 배출하는 반복적이고 부적절한 보상 행동.
+체크리스트 그룹: body_image_cognition (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 체형/체중 이미지 왜곡: 체중이나 체형이 자기평가에 지나친 영향을 미침.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D022_S001_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D022_S001_P002__claude-sonnet-5_kor.xlsx
@@ -754,6 +754,11 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -798,11 +803,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D022_S001_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D022_S001_P002__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.3958</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.8889</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
